--- a/docs/velli-bi/plantilla-precios.xlsx
+++ b/docs/velli-bi/plantilla-precios.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cómo usarla" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servicios" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ajustes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumo" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comisiones" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulador" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Cómo usarla" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Servicios" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ajustes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Productos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Consumo" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Comisiones" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Simulador" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Registro" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Resumen" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Servicios'!$8:$8</definedName>
@@ -314,7 +314,7 @@
     </comment>
     <comment ref="C12" authorId="0" shapeId="0">
       <text>
-        <t>Regla propuesta por Velli para clasificar la fibra; la valida Keila (docs/velli-bi/02, §1.1).</t>
+        <t>Estándar de Velli para clasificar la fibra (docs/velli-bi/02, §1.1). Ajústalo si el salón usa otro criterio.</t>
       </text>
     </comment>
   </commentList>
@@ -335,6 +335,11 @@
     <comment ref="C7" authorId="0" shapeId="0">
       <text>
         <t>Factores de partida propuestos por Velli, no medidos. Ajústalos con el salón: 2 = el doble de tinte que un cabello corto.</t>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0">
+      <text>
+        <t>Estándar de Velli: con 50–75 % de canas se gasta 15 % más de producto por saturación; con 75–100 %, 20 % más.</t>
       </text>
     </comment>
   </commentList>
@@ -630,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -809,29 +814,61 @@
       <c r="A21" s="2" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Privacidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
+          <t>Estándares de Velli (se pueden ajustar con el salón)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
       <c r="A22" s="2" t="n"/>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>En Registro escribe solo las iniciales de la clienta. No anotes datos de salud capilar ni del diagnóstico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
+          <t>Largo: corto (mentón), medio (hombros o clavícula), largo (media espalda o tira del brasier), extra largo (cintura o más).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
       <c r="A23" s="2" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Fuente del modelo</t>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Estado de la fibra: sana o virgen (sin recargo); procesada o porosa (sugerir un tratamiento sellante); sensibilizada o muy dañada (prueba de mechón y aditivo protector Plex obligatorios en servicios químicos).</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="2" t="n"/>
       <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Canas: 0–25 %, 25–50 %, 50–75 % (+15 % de producto por saturación) y 75–100 % (+20 % de producto y técnica de prepigmentación).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Privacidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>En Registro escribe solo las iniciales de la clienta. No anotes datos de salud capilar ni del diagnóstico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Fuente del modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>docs/velli-bi/02-diseno-cotizador.md (secciones 1.1, 1.2 y 3). Precio = redondeo((base + sumas) × (1 + porcentajes)).</t>
         </is>
@@ -886,7 +923,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Precio base = lo que cobra el salón con cabello corto, densidad media, fibra sana y sin canas. Las columnas «Ajusta por…» dicen qué variables cambian el precio de ese servicio.</t>
+          <t>Precio base = lo que cobra el salón con cabello corto, densidad media, fibra sana y hasta 25 % de canas. Las columnas «Ajusta por…» dicen qué variables cambian el precio de ese servicio.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1605,7 +1642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1629,7 +1666,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Cuánto sube el precio según cada variable. Puedes usar suma fija, porcentaje o ambos: precio = (base + sumas) × (1 + porcentajes). El valor de referencia (corto, media, sano, sin canas) siempre es 0.</t>
+          <t>Cuánto sube el precio según cada variable. Puedes usar suma fija, porcentaje o ambos: precio = (base + sumas) × (1 + porcentajes). El valor de referencia (corto, media, sana, 0–25 % de canas) siempre es 0.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1707,7 +1744,7 @@
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>Hasta los hombros</t>
+          <t>Hasta los hombros o la clavícula</t>
         </is>
       </c>
       <c r="D6" s="11" t="n">
@@ -1730,7 +1767,7 @@
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>Hasta los omóplatos</t>
+          <t>Hasta la media espalda o la tira del brasier</t>
         </is>
       </c>
       <c r="D7" s="11" t="n">
@@ -1840,12 +1877,12 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>Sano</t>
+          <t>Sana / virgen</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>Puntas sanas, sin daño, buena elasticidad (referencia)</t>
+          <t>Sin química previa ni daño, buena elasticidad (referencia, sin recargo)</t>
         </is>
       </c>
       <c r="D12" s="19" t="n">
@@ -1863,12 +1900,12 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Sensibilizado</t>
+          <t>Procesada / porosa</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>Puntas abiertas leves, daño mecánico o térmico, o elasticidad media</t>
+          <t>Química previa (tinte, decoloración, alisado), porosidad alta o daño leve. Sugerir un tratamiento sellante</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
@@ -1886,12 +1923,12 @@
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>Comprometido</t>
+          <t>Sensibilizada / muy dañada</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>Puntas abiertas severas, daño químico o elasticidad baja</t>
+          <t>Elasticidad baja, puntas abiertas severas o daño químico. En químicos: prueba de mechón y aditivo Plex obligatorios</t>
         </is>
       </c>
       <c r="D14" s="11" t="n">
@@ -1909,12 +1946,12 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Sin canas</t>
+          <t>0–25 %</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>Referencia</t>
+          <t>Sin canas o canas sueltas (referencia)</t>
         </is>
       </c>
       <c r="D15" s="19" t="n">
@@ -1932,16 +1969,16 @@
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>Menos del 25 %</t>
+          <t>25–50 %</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>Canas sueltas</t>
+          <t>Hasta la mitad</t>
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E16" s="21" t="n">
         <v>0</v>
@@ -1955,16 +1992,16 @@
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>25–50 %</t>
+          <t>50–75 %</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>Hasta la mitad</t>
+          <t>Más de la mitad. +15 % de producto por saturación</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="E17" s="21" t="n">
         <v>0</v>
@@ -1978,41 +2015,18 @@
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>50–75 %</t>
+          <t>75–100 %</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>Más de la mitad</t>
+          <t>Casi todo cano. +20 % de producto y técnica de prepigmentación</t>
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>Canas</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>Más del 75 %</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>Casi todo cano</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E19" s="21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2586,7 +2600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2606,7 +2620,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>La calculadora de color de Velli formula un tubo (60 g por defecto). Aquí el salón dice cuánto más gasta según el largo y la densidad. Pregúntale a la estilista que más color hace.</t>
+          <t>La calculadora de color de Velli formula un tubo (60 g por defecto). Aquí el salón dice cuánto más gasta según el largo, la densidad y las canas. Pregúntale a la estilista que más color hace.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2746,6 +2760,62 @@
       </c>
       <c r="C13" s="22" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Canas</t>
+        </is>
+      </c>
+      <c r="B14" s="7">
+        <f>Ajustes!B15</f>
+        <v/>
+      </c>
+      <c r="C14" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Canas</t>
+        </is>
+      </c>
+      <c r="B15" s="7">
+        <f>Ajustes!B16</f>
+        <v/>
+      </c>
+      <c r="C15" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>Canas</t>
+        </is>
+      </c>
+      <c r="B16" s="7">
+        <f>Ajustes!B17</f>
+        <v/>
+      </c>
+      <c r="C16" s="22" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Canas</t>
+        </is>
+      </c>
+      <c r="B17" s="7">
+        <f>Ajustes!B18</f>
+        <v/>
+      </c>
+      <c r="C17" s="22" t="n">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -3051,7 +3121,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Sano</t>
+          <t>Sana / virgen</t>
         </is>
       </c>
       <c r="C7" s="2" t="n"/>
@@ -3153,7 +3223,7 @@
         </is>
       </c>
       <c r="B16" s="19">
-        <f>IF($B$14=0,0,IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$B$5),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$B$6),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$B$7),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$B$8),0))</f>
+        <f>IF($B$14=0,0,IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$B$5),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$B$6),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$B$7),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$B$8),0))</f>
         <v/>
       </c>
       <c r="C16" s="26" t="inlineStr">
@@ -3169,7 +3239,7 @@
         </is>
       </c>
       <c r="B17" s="20">
-        <f>IF($B$14=0,0,IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$B$5),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$B$6),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$B$7),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$B$8),0))</f>
+        <f>IF($B$14=0,0,IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$B$5),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$B$6),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$B$7),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$B$8),0))</f>
         <v/>
       </c>
       <c r="C17" s="26" t="inlineStr">
@@ -3197,7 +3267,7 @@
         </is>
       </c>
       <c r="B19" s="27">
-        <f>IF($B$14=0,0,ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$B$14))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$B$5),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$B$6),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$B$7),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$B$8),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$B$5),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$B$6),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$B$7),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$B$8),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($B$14=0,0,ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$B$14))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$B$5),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$B$6),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$B$7),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$B$8),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$B$5),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$B$6),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$B$7),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$B$14))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$B$8),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="C19" s="26" t="inlineStr">
@@ -3219,9 +3289,20 @@
       <c r="C20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Avisos del estándar</t>
+        </is>
+      </c>
+      <c r="B21" s="6">
+        <f>IF($B$14=0,"",IF(AND($B$7="Sensibilizada / muy dañada",OR(INDEX(Servicios!$B$9:$B$38,MAX(1,$B$14))="color",INDEX(Servicios!$B$9:$B$38,MAX(1,$B$14))="decoloración",INDEX(Servicios!$B$9:$B$38,MAX(1,$B$14))="alisado")),"Obligatorio: prueba de mechón y aditivo protector Plex.","")&amp;IF($B$7="Procesada / porosa","Sugerir un tratamiento sellante.","")&amp;IF(AND(OR(AND($B$7="Sensibilizada / muy dañada",OR(INDEX(Servicios!$B$9:$B$38,MAX(1,$B$14))="color",INDEX(Servicios!$B$9:$B$38,MAX(1,$B$14))="decoloración",INDEX(Servicios!$B$9:$B$38,MAX(1,$B$14))="alisado")),$B$7="Procesada / porosa"),AND($B$8="75–100 %",B23="Sí"))," ","")&amp;IF(AND($B$8="75–100 %",B23="Sí"),"Técnica de prepigmentación.",""))</f>
+        <v/>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Del estándar de Velli: estado de la fibra y canas. La prueba de mechón aplica a servicios químicos.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="24" t="inlineStr">
@@ -3263,7 +3344,7 @@
         </is>
       </c>
       <c r="B25" s="30">
-        <f>SUMIFS(Consumo!$C$7:$C$13,Consumo!$A$7:$A$13,"Largo",Consumo!$B$7:$B$13,$B$5)</f>
+        <f>SUMIFS(Consumo!$C$7:$C$17,Consumo!$A$7:$A$17,"Largo",Consumo!$B$7:$B$17,$B$5)</f>
         <v/>
       </c>
       <c r="C25" s="2" t="n"/>
@@ -3275,7 +3356,7 @@
         </is>
       </c>
       <c r="B26" s="30">
-        <f>SUMIFS(Consumo!$C$7:$C$13,Consumo!$A$7:$A$13,"Densidad",Consumo!$B$7:$B$13,$B$6)</f>
+        <f>SUMIFS(Consumo!$C$7:$C$17,Consumo!$A$7:$A$17,"Densidad",Consumo!$B$7:$B$17,$B$6)</f>
         <v/>
       </c>
       <c r="C26" s="2" t="n"/>
@@ -3283,39 +3364,43 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Gramos de tinte estimados</t>
-        </is>
-      </c>
-      <c r="B27" s="29">
-        <f>IF(B23="Sí",B24*B25*B26,0)</f>
+          <t>Factor por canas</t>
+        </is>
+      </c>
+      <c r="B27" s="30">
+        <f>SUMIFS(Consumo!$C$7:$C$17,Consumo!$A$7:$A$17,"Canas",Consumo!$B$7:$B$17,$B$8)</f>
         <v/>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Gramos base × factor por largo × factor por densidad.</t>
+          <t>Estándar: 50–75 % de canas suma 15 % de producto; 75–100 %, 20 %.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Costo del tinte</t>
-        </is>
-      </c>
-      <c r="B28" s="19">
-        <f>B27*IFERROR(INDEX(Productos!$G$5:$G$34,MATCH($B$10,Productos!$A$5:$A$34,0)),0)</f>
-        <v/>
-      </c>
-      <c r="C28" s="2" t="n"/>
+          <t>Gramos de tinte estimados</t>
+        </is>
+      </c>
+      <c r="B28" s="29">
+        <f>IF(B23="Sí",B24*B25*B26*B27,0)</f>
+        <v/>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Gramos base × factor por largo × factor por densidad × factor por canas.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Mililitros de oxidante</t>
-        </is>
-      </c>
-      <c r="B29" s="29">
-        <f>B27*Consumo!$B$4</f>
+          <t>Costo del tinte</t>
+        </is>
+      </c>
+      <c r="B29" s="19">
+        <f>B28*IFERROR(INDEX(Productos!$G$5:$G$34,MATCH($B$10,Productos!$A$5:$A$34,0)),0)</f>
         <v/>
       </c>
       <c r="C29" s="2" t="n"/>
@@ -3323,11 +3408,11 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Costo del oxidante</t>
-        </is>
-      </c>
-      <c r="B30" s="19">
-        <f>B29*IFERROR(INDEX(Productos!$G$5:$G$34,MATCH($B$11,Productos!$A$5:$A$34,0)),0)</f>
+          <t>Mililitros de oxidante</t>
+        </is>
+      </c>
+      <c r="B30" s="29">
+        <f>B28*Consumo!$B$4</f>
         <v/>
       </c>
       <c r="C30" s="2" t="n"/>
@@ -3335,30 +3420,37 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>Costo del oxidante</t>
+        </is>
+      </c>
+      <c r="B31" s="19">
+        <f>B30*IFERROR(INDEX(Productos!$G$5:$G$34,MATCH($B$11,Productos!$A$5:$A$34,0)),0)</f>
+        <v/>
+      </c>
+      <c r="C31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>Insumos fijos</t>
         </is>
       </c>
-      <c r="B31" s="19">
+      <c r="B32" s="19">
         <f>IF($B$14=0,0,IF(ISNUMBER(INDEX(Servicios!$J$9:$J$38,MAX(1,$B$14))),INDEX(Servicios!$J$9:$J$38,MAX(1,$B$14)),0))</f>
         <v/>
       </c>
-      <c r="C31" s="2" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="C32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Costo total de producto</t>
         </is>
       </c>
-      <c r="B32" s="27">
-        <f>B28+B30+B31</f>
-        <v/>
-      </c>
-      <c r="C32" s="2" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="B33" s="27">
+        <f>B29+B31+B32</f>
+        <v/>
+      </c>
       <c r="C33" s="2" t="n"/>
     </row>
     <row r="34">
@@ -3417,7 +3509,7 @@
         </is>
       </c>
       <c r="B38" s="19">
-        <f>B36*IF(B37="Precio menos producto",B19-B32,B19)</f>
+        <f>B36*IF(B37="Precio menos producto",B19-B33,B19)</f>
         <v/>
       </c>
       <c r="C38" s="2" t="n"/>
@@ -3429,7 +3521,7 @@
         </is>
       </c>
       <c r="B39" s="27">
-        <f>B19-B32-B38</f>
+        <f>B19-B33-B38</f>
         <v/>
       </c>
       <c r="C39" s="26" t="inlineStr">
@@ -3468,7 +3560,7 @@
       <formula1>Ajustes!$B$12:$B$14</formula1>
     </dataValidation>
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista." type="list">
-      <formula1>Ajustes!$B$15:$B$19</formula1>
+      <formula1>Ajustes!$B$15:$B$18</formula1>
     </dataValidation>
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista." type="list">
       <formula1>Comisiones!$A$5:$A$19</formula1>
@@ -3657,7 +3749,7 @@
     </row>
     <row r="5">
       <c r="A5" s="31" t="n">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
@@ -3686,7 +3778,7 @@
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>Sano</t>
+          <t>Sana / virgen</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
@@ -3695,7 +3787,7 @@
         </is>
       </c>
       <c r="I5" s="19">
-        <f>IF($O5=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O5))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O5))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E5),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O5))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F5),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O5))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G5),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O5))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H5),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O5))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E5),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O5))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F5),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O5))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G5),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O5))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H5),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O5=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O5))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O5))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E5),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O5))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F5),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O5))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G5),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O5))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H5),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O5))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E5),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O5))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F5),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O5))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G5),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O5))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H5),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J5" s="15" t="n">
@@ -3734,7 +3826,7 @@
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="19">
-        <f>IF($O6=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O6))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O6))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E6),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O6))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F6),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O6))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G6),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O6))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H6),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O6))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E6),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O6))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F6),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O6))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G6),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O6))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H6),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O6=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O6))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O6))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E6),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O6))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F6),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O6))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G6),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O6))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H6),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O6))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E6),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O6))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F6),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O6))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G6),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O6))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H6),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J6" s="11" t="n"/>
@@ -3767,7 +3859,7 @@
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="19">
-        <f>IF($O7=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O7))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O7))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E7),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O7))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F7),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O7))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G7),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O7))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H7),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O7))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E7),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O7))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F7),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O7))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G7),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O7))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H7),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O7=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O7))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O7))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E7),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O7))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F7),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O7))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G7),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O7))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H7),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O7))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E7),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O7))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F7),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O7))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G7),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O7))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H7),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J7" s="11" t="n"/>
@@ -3800,7 +3892,7 @@
       <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="19">
-        <f>IF($O8=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O8))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O8))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E8),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O8))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F8),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O8))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G8),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O8))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H8),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O8))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E8),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O8))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F8),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O8))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G8),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O8))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H8),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O8=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O8))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O8))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E8),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O8))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F8),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O8))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G8),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O8))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H8),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O8))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E8),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O8))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F8),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O8))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G8),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O8))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H8),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J8" s="11" t="n"/>
@@ -3833,7 +3925,7 @@
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="19">
-        <f>IF($O9=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O9))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O9))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E9),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O9))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F9),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O9))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G9),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O9))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H9),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O9))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E9),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O9))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F9),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O9))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G9),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O9))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H9),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O9=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O9))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O9))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E9),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O9))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F9),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O9))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G9),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O9))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H9),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O9))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E9),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O9))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F9),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O9))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G9),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O9))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H9),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J9" s="11" t="n"/>
@@ -3866,7 +3958,7 @@
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="19">
-        <f>IF($O10=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O10))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O10))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E10),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O10))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F10),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O10))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G10),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O10))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H10),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O10))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E10),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O10))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F10),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O10))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G10),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O10))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H10),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O10=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O10))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O10))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E10),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O10))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F10),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O10))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G10),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O10))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H10),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O10))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E10),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O10))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F10),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O10))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G10),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O10))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H10),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J10" s="11" t="n"/>
@@ -3899,7 +3991,7 @@
       <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="19">
-        <f>IF($O11=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O11))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O11))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E11),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O11))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F11),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O11))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G11),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O11))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H11),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O11))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E11),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O11))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F11),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O11))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G11),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O11))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H11),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O11=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O11))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O11))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E11),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O11))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F11),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O11))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G11),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O11))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H11),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O11))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E11),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O11))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F11),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O11))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G11),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O11))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H11),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J11" s="11" t="n"/>
@@ -3932,7 +4024,7 @@
       <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="19">
-        <f>IF($O12=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O12))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O12))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E12),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O12))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F12),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O12))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G12),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O12))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H12),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O12))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E12),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O12))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F12),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O12))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G12),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O12))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H12),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O12=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O12))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O12))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E12),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O12))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F12),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O12))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G12),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O12))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H12),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O12))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E12),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O12))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F12),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O12))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G12),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O12))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H12),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J12" s="11" t="n"/>
@@ -3965,7 +4057,7 @@
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="19">
-        <f>IF($O13=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O13))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O13))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E13),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O13))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F13),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O13))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G13),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O13))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H13),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O13))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E13),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O13))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F13),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O13))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G13),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O13))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H13),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O13=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O13))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O13))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E13),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O13))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F13),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O13))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G13),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O13))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H13),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O13))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E13),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O13))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F13),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O13))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G13),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O13))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H13),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J13" s="11" t="n"/>
@@ -3998,7 +4090,7 @@
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="19">
-        <f>IF($O14=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O14))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O14))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E14),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O14))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F14),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O14))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G14),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O14))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H14),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O14))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E14),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O14))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F14),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O14))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G14),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O14))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H14),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O14=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O14))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O14))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E14),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O14))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F14),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O14))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G14),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O14))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H14),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O14))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E14),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O14))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F14),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O14))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G14),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O14))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H14),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J14" s="11" t="n"/>
@@ -4031,7 +4123,7 @@
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="19">
-        <f>IF($O15=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O15))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O15))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E15),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O15))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F15),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O15))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G15),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O15))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H15),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O15))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E15),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O15))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F15),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O15))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G15),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O15))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H15),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O15=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O15))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O15))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E15),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O15))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F15),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O15))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G15),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O15))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H15),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O15))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E15),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O15))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F15),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O15))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G15),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O15))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H15),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J15" s="11" t="n"/>
@@ -4064,7 +4156,7 @@
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="19">
-        <f>IF($O16=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O16))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O16))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E16),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O16))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F16),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O16))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G16),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O16))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H16),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O16))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E16),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O16))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F16),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O16))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G16),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O16))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H16),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O16=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O16))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O16))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E16),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O16))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F16),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O16))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G16),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O16))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H16),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O16))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E16),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O16))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F16),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O16))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G16),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O16))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H16),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J16" s="11" t="n"/>
@@ -4097,7 +4189,7 @@
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="19">
-        <f>IF($O17=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O17))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O17))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E17),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O17))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F17),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O17))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G17),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O17))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H17),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O17))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E17),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O17))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F17),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O17))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G17),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O17))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H17),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O17=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O17))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O17))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E17),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O17))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F17),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O17))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G17),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O17))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H17),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O17))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E17),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O17))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F17),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O17))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G17),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O17))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H17),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J17" s="11" t="n"/>
@@ -4130,7 +4222,7 @@
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="19">
-        <f>IF($O18=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O18))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O18))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E18),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O18))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F18),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O18))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G18),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O18))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H18),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O18))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E18),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O18))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F18),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O18))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G18),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O18))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H18),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O18=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O18))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O18))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E18),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O18))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F18),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O18))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G18),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O18))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H18),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O18))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E18),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O18))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F18),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O18))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G18),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O18))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H18),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J18" s="11" t="n"/>
@@ -4163,7 +4255,7 @@
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="19">
-        <f>IF($O19=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O19))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O19))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E19),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O19))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F19),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O19))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G19),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O19))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H19),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O19))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E19),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O19))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F19),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O19))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G19),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O19))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H19),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O19=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O19))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O19))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E19),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O19))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F19),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O19))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G19),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O19))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H19),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O19))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E19),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O19))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F19),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O19))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G19),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O19))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H19),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J19" s="11" t="n"/>
@@ -4196,7 +4288,7 @@
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="19">
-        <f>IF($O20=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O20))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O20))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E20),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O20))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F20),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O20))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G20),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O20))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H20),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O20))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E20),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O20))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F20),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O20))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G20),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O20))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H20),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O20=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O20))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O20))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E20),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O20))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F20),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O20))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G20),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O20))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H20),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O20))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E20),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O20))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F20),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O20))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G20),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O20))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H20),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J20" s="11" t="n"/>
@@ -4229,7 +4321,7 @@
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="19">
-        <f>IF($O21=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O21))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O21))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E21),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O21))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F21),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O21))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G21),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O21))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H21),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O21))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E21),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O21))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F21),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O21))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G21),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O21))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H21),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O21=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O21))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O21))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E21),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O21))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F21),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O21))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G21),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O21))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H21),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O21))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E21),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O21))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F21),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O21))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G21),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O21))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H21),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J21" s="11" t="n"/>
@@ -4262,7 +4354,7 @@
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="19">
-        <f>IF($O22=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O22))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O22))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E22),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O22))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F22),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O22))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G22),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O22))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H22),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O22))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E22),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O22))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F22),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O22))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G22),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O22))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H22),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O22=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O22))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O22))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E22),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O22))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F22),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O22))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G22),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O22))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H22),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O22))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E22),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O22))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F22),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O22))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G22),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O22))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H22),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J22" s="11" t="n"/>
@@ -4295,7 +4387,7 @@
       <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="19">
-        <f>IF($O23=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O23))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O23))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E23),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O23))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F23),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O23))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G23),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O23))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H23),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O23))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E23),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O23))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F23),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O23))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G23),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O23))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H23),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O23=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O23))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O23))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E23),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O23))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F23),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O23))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G23),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O23))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H23),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O23))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E23),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O23))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F23),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O23))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G23),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O23))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H23),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J23" s="11" t="n"/>
@@ -4328,7 +4420,7 @@
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="19">
-        <f>IF($O24=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O24))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O24))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E24),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O24))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F24),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O24))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G24),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O24))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H24),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O24))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E24),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O24))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F24),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O24))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G24),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O24))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H24),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O24=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O24))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O24))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E24),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O24))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F24),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O24))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G24),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O24))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H24),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O24))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E24),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O24))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F24),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O24))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G24),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O24))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H24),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J24" s="11" t="n"/>
@@ -4361,7 +4453,7 @@
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="19">
-        <f>IF($O25=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O25))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O25))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E25),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O25))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F25),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O25))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G25),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O25))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H25),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O25))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E25),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O25))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F25),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O25))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G25),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O25))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H25),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O25=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O25))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O25))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E25),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O25))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F25),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O25))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G25),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O25))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H25),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O25))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E25),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O25))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F25),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O25))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G25),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O25))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H25),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J25" s="11" t="n"/>
@@ -4394,7 +4486,7 @@
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="19">
-        <f>IF($O26=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O26))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O26))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E26),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O26))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F26),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O26))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G26),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O26))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H26),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O26))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E26),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O26))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F26),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O26))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G26),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O26))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H26),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O26=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O26))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O26))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E26),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O26))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F26),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O26))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G26),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O26))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H26),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O26))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E26),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O26))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F26),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O26))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G26),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O26))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H26),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J26" s="11" t="n"/>
@@ -4427,7 +4519,7 @@
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="19">
-        <f>IF($O27=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O27))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O27))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E27),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O27))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F27),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O27))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G27),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O27))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H27),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O27))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E27),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O27))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F27),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O27))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G27),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O27))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H27),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O27=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O27))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O27))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E27),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O27))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F27),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O27))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G27),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O27))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H27),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O27))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E27),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O27))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F27),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O27))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G27),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O27))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H27),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J27" s="11" t="n"/>
@@ -4460,7 +4552,7 @@
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="19">
-        <f>IF($O28=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O28))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O28))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E28),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O28))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F28),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O28))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G28),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O28))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H28),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O28))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E28),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O28))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F28),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O28))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G28),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O28))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H28),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O28=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O28))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O28))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E28),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O28))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F28),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O28))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G28),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O28))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H28),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O28))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E28),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O28))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F28),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O28))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G28),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O28))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H28),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J28" s="11" t="n"/>
@@ -4493,7 +4585,7 @@
       <c r="G29" s="5" t="n"/>
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="19">
-        <f>IF($O29=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O29))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O29))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E29),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O29))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F29),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O29))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G29),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O29))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H29),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O29))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E29),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O29))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F29),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O29))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G29),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O29))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H29),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O29=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O29))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O29))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E29),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O29))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F29),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O29))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G29),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O29))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H29),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O29))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E29),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O29))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F29),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O29))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G29),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O29))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H29),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J29" s="11" t="n"/>
@@ -4526,7 +4618,7 @@
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="19">
-        <f>IF($O30=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O30))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O30))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E30),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O30))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F30),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O30))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G30),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O30))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H30),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O30))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E30),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O30))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F30),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O30))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G30),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O30))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H30),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O30=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O30))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O30))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E30),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O30))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F30),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O30))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G30),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O30))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H30),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O30))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E30),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O30))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F30),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O30))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G30),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O30))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H30),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J30" s="11" t="n"/>
@@ -4559,7 +4651,7 @@
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="19">
-        <f>IF($O31=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O31))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O31))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E31),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O31))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F31),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O31))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G31),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O31))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H31),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O31))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E31),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O31))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F31),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O31))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G31),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O31))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H31),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O31=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O31))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O31))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E31),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O31))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F31),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O31))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G31),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O31))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H31),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O31))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E31),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O31))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F31),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O31))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G31),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O31))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H31),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J31" s="11" t="n"/>
@@ -4592,7 +4684,7 @@
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="19">
-        <f>IF($O32=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O32))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O32))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E32),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O32))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F32),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O32))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G32),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O32))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H32),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O32))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E32),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O32))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F32),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O32))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G32),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O32))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H32),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O32=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O32))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O32))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E32),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O32))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F32),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O32))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G32),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O32))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H32),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O32))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E32),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O32))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F32),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O32))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G32),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O32))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H32),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J32" s="11" t="n"/>
@@ -4625,7 +4717,7 @@
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="19">
-        <f>IF($O33=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O33))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O33))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E33),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O33))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F33),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O33))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G33),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O33))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H33),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O33))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E33),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O33))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F33),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O33))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G33),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O33))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H33),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O33=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O33))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O33))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E33),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O33))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F33),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O33))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G33),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O33))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H33),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O33))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E33),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O33))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F33),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O33))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G33),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O33))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H33),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J33" s="11" t="n"/>
@@ -4658,7 +4750,7 @@
       <c r="G34" s="5" t="n"/>
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="19">
-        <f>IF($O34=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O34))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O34))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E34),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O34))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F34),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O34))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G34),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O34))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H34),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O34))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E34),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O34))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F34),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O34))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G34),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O34))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H34),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O34=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O34))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O34))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E34),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O34))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F34),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O34))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G34),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O34))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H34),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O34))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E34),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O34))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F34),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O34))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G34),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O34))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H34),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J34" s="11" t="n"/>
@@ -4691,7 +4783,7 @@
       <c r="G35" s="5" t="n"/>
       <c r="H35" s="5" t="n"/>
       <c r="I35" s="19">
-        <f>IF($O35=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O35))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O35))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E35),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O35))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F35),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O35))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G35),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O35))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H35),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O35))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E35),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O35))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F35),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O35))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G35),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O35))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H35),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O35=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O35))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O35))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E35),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O35))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F35),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O35))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G35),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O35))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H35),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O35))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E35),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O35))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F35),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O35))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G35),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O35))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H35),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J35" s="11" t="n"/>
@@ -4724,7 +4816,7 @@
       <c r="G36" s="5" t="n"/>
       <c r="H36" s="5" t="n"/>
       <c r="I36" s="19">
-        <f>IF($O36=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O36))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O36))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E36),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O36))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F36),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O36))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G36),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O36))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H36),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O36))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E36),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O36))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F36),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O36))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G36),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O36))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H36),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O36=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O36))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O36))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E36),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O36))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F36),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O36))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G36),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O36))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H36),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O36))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E36),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O36))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F36),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O36))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G36),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O36))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H36),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J36" s="11" t="n"/>
@@ -4757,7 +4849,7 @@
       <c r="G37" s="5" t="n"/>
       <c r="H37" s="5" t="n"/>
       <c r="I37" s="19">
-        <f>IF($O37=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O37))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O37))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E37),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O37))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F37),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O37))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G37),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O37))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H37),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O37))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E37),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O37))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F37),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O37))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G37),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O37))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H37),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O37=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O37))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O37))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E37),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O37))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F37),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O37))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G37),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O37))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H37),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O37))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E37),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O37))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F37),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O37))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G37),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O37))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H37),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J37" s="11" t="n"/>
@@ -4790,7 +4882,7 @@
       <c r="G38" s="5" t="n"/>
       <c r="H38" s="5" t="n"/>
       <c r="I38" s="19">
-        <f>IF($O38=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O38))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O38))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E38),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O38))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F38),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O38))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G38),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O38))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H38),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O38))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E38),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O38))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F38),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O38))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G38),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O38))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H38),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O38=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O38))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O38))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E38),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O38))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F38),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O38))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G38),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O38))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H38),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O38))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E38),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O38))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F38),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O38))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G38),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O38))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H38),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J38" s="11" t="n"/>
@@ -4823,7 +4915,7 @@
       <c r="G39" s="5" t="n"/>
       <c r="H39" s="5" t="n"/>
       <c r="I39" s="19">
-        <f>IF($O39=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O39))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O39))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E39),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O39))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F39),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O39))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G39),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O39))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H39),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O39))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E39),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O39))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F39),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O39))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G39),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O39))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H39),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O39=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O39))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O39))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E39),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O39))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F39),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O39))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G39),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O39))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H39),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O39))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E39),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O39))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F39),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O39))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G39),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O39))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H39),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J39" s="11" t="n"/>
@@ -4856,7 +4948,7 @@
       <c r="G40" s="5" t="n"/>
       <c r="H40" s="5" t="n"/>
       <c r="I40" s="19">
-        <f>IF($O40=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O40))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O40))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E40),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O40))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F40),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O40))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G40),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O40))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H40),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O40))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E40),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O40))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F40),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O40))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G40),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O40))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H40),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O40=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O40))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O40))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E40),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O40))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F40),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O40))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G40),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O40))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H40),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O40))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E40),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O40))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F40),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O40))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G40),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O40))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H40),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J40" s="11" t="n"/>
@@ -4889,7 +4981,7 @@
       <c r="G41" s="5" t="n"/>
       <c r="H41" s="5" t="n"/>
       <c r="I41" s="19">
-        <f>IF($O41=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O41))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O41))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E41),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O41))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F41),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O41))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G41),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O41))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H41),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O41))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E41),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O41))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F41),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O41))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G41),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O41))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H41),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O41=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O41))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O41))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E41),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O41))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F41),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O41))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G41),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O41))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H41),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O41))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E41),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O41))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F41),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O41))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G41),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O41))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H41),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J41" s="11" t="n"/>
@@ -4922,7 +5014,7 @@
       <c r="G42" s="5" t="n"/>
       <c r="H42" s="5" t="n"/>
       <c r="I42" s="19">
-        <f>IF($O42=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O42))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O42))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E42),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O42))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F42),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O42))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G42),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O42))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H42),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O42))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E42),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O42))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F42),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O42))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G42),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O42))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H42),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O42=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O42))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O42))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E42),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O42))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F42),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O42))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G42),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O42))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H42),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O42))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E42),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O42))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F42),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O42))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G42),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O42))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H42),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J42" s="11" t="n"/>
@@ -4955,7 +5047,7 @@
       <c r="G43" s="5" t="n"/>
       <c r="H43" s="5" t="n"/>
       <c r="I43" s="19">
-        <f>IF($O43=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O43))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O43))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E43),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O43))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F43),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O43))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G43),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O43))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H43),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O43))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E43),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O43))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F43),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O43))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G43),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O43))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H43),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O43=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O43))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O43))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E43),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O43))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F43),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O43))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G43),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O43))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H43),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O43))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E43),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O43))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F43),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O43))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G43),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O43))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H43),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J43" s="11" t="n"/>
@@ -4988,7 +5080,7 @@
       <c r="G44" s="5" t="n"/>
       <c r="H44" s="5" t="n"/>
       <c r="I44" s="19">
-        <f>IF($O44=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O44))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O44))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E44),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O44))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F44),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O44))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G44),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O44))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H44),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O44))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E44),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O44))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F44),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O44))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G44),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O44))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H44),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O44=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O44))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O44))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E44),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O44))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F44),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O44))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G44),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O44))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H44),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O44))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E44),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O44))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F44),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O44))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G44),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O44))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H44),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J44" s="11" t="n"/>
@@ -5021,7 +5113,7 @@
       <c r="G45" s="5" t="n"/>
       <c r="H45" s="5" t="n"/>
       <c r="I45" s="19">
-        <f>IF($O45=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O45))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O45))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E45),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O45))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F45),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O45))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G45),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O45))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H45),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O45))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E45),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O45))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F45),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O45))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G45),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O45))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H45),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O45=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O45))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O45))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E45),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O45))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F45),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O45))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G45),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O45))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H45),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O45))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E45),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O45))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F45),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O45))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G45),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O45))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H45),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J45" s="11" t="n"/>
@@ -5054,7 +5146,7 @@
       <c r="G46" s="5" t="n"/>
       <c r="H46" s="5" t="n"/>
       <c r="I46" s="19">
-        <f>IF($O46=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O46))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O46))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E46),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O46))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F46),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O46))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G46),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O46))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H46),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O46))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E46),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O46))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F46),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O46))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G46),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O46))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H46),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O46=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O46))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O46))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E46),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O46))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F46),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O46))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G46),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O46))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H46),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O46))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E46),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O46))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F46),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O46))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G46),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O46))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H46),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J46" s="11" t="n"/>
@@ -5087,7 +5179,7 @@
       <c r="G47" s="5" t="n"/>
       <c r="H47" s="5" t="n"/>
       <c r="I47" s="19">
-        <f>IF($O47=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O47))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O47))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E47),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O47))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F47),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O47))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G47),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O47))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H47),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O47))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E47),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O47))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F47),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O47))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G47),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O47))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H47),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O47=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O47))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O47))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E47),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O47))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F47),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O47))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G47),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O47))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H47),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O47))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E47),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O47))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F47),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O47))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G47),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O47))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H47),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J47" s="11" t="n"/>
@@ -5120,7 +5212,7 @@
       <c r="G48" s="5" t="n"/>
       <c r="H48" s="5" t="n"/>
       <c r="I48" s="19">
-        <f>IF($O48=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O48))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O48))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E48),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O48))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F48),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O48))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G48),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O48))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H48),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O48))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E48),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O48))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F48),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O48))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G48),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O48))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H48),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O48=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O48))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O48))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E48),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O48))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F48),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O48))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G48),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O48))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H48),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O48))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E48),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O48))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F48),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O48))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G48),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O48))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H48),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J48" s="11" t="n"/>
@@ -5153,7 +5245,7 @@
       <c r="G49" s="5" t="n"/>
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="19">
-        <f>IF($O49=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O49))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O49))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E49),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O49))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F49),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O49))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G49),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O49))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H49),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O49))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E49),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O49))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F49),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O49))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G49),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O49))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H49),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O49=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O49))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O49))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E49),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O49))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F49),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O49))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G49),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O49))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H49),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O49))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E49),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O49))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F49),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O49))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G49),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O49))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H49),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J49" s="11" t="n"/>
@@ -5186,7 +5278,7 @@
       <c r="G50" s="5" t="n"/>
       <c r="H50" s="5" t="n"/>
       <c r="I50" s="19">
-        <f>IF($O50=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O50))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O50))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E50),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O50))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F50),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O50))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G50),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O50))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H50),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O50))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E50),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O50))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F50),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O50))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G50),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O50))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H50),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O50=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O50))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O50))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E50),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O50))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F50),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O50))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G50),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O50))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H50),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O50))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E50),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O50))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F50),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O50))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G50),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O50))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H50),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J50" s="11" t="n"/>
@@ -5219,7 +5311,7 @@
       <c r="G51" s="5" t="n"/>
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="19">
-        <f>IF($O51=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O51))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O51))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E51),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O51))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F51),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O51))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G51),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O51))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H51),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O51))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E51),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O51))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F51),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O51))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G51),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O51))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H51),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O51=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O51))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O51))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E51),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O51))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F51),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O51))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G51),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O51))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H51),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O51))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E51),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O51))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F51),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O51))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G51),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O51))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H51),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J51" s="11" t="n"/>
@@ -5252,7 +5344,7 @@
       <c r="G52" s="5" t="n"/>
       <c r="H52" s="5" t="n"/>
       <c r="I52" s="19">
-        <f>IF($O52=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O52))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O52))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E52),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O52))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F52),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O52))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G52),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O52))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H52),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O52))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E52),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O52))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F52),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O52))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G52),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O52))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H52),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O52=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O52))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O52))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E52),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O52))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F52),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O52))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G52),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O52))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H52),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O52))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E52),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O52))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F52),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O52))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G52),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O52))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H52),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J52" s="11" t="n"/>
@@ -5285,7 +5377,7 @@
       <c r="G53" s="5" t="n"/>
       <c r="H53" s="5" t="n"/>
       <c r="I53" s="19">
-        <f>IF($O53=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O53))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O53))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E53),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O53))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F53),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O53))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G53),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O53))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H53),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O53))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E53),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O53))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F53),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O53))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G53),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O53))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H53),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O53=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O53))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O53))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E53),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O53))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F53),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O53))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G53),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O53))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H53),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O53))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E53),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O53))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F53),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O53))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G53),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O53))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H53),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J53" s="11" t="n"/>
@@ -5318,7 +5410,7 @@
       <c r="G54" s="5" t="n"/>
       <c r="H54" s="5" t="n"/>
       <c r="I54" s="19">
-        <f>IF($O54=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O54))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O54))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E54),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O54))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F54),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O54))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G54),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O54))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H54),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O54))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E54),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O54))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F54),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O54))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G54),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O54))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H54),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O54=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O54))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O54))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E54),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O54))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F54),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O54))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G54),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O54))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H54),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O54))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E54),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O54))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F54),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O54))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G54),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O54))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H54),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J54" s="11" t="n"/>
@@ -5351,7 +5443,7 @@
       <c r="G55" s="5" t="n"/>
       <c r="H55" s="5" t="n"/>
       <c r="I55" s="19">
-        <f>IF($O55=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O55))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O55))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E55),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O55))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F55),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O55))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G55),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O55))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H55),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O55))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E55),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O55))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F55),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O55))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G55),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O55))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H55),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O55=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O55))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O55))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E55),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O55))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F55),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O55))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G55),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O55))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H55),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O55))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E55),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O55))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F55),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O55))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G55),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O55))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H55),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J55" s="11" t="n"/>
@@ -5384,7 +5476,7 @@
       <c r="G56" s="5" t="n"/>
       <c r="H56" s="5" t="n"/>
       <c r="I56" s="19">
-        <f>IF($O56=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O56))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O56))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E56),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O56))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F56),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O56))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G56),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O56))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H56),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O56))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E56),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O56))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F56),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O56))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G56),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O56))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H56),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O56=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O56))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O56))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E56),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O56))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F56),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O56))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G56),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O56))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H56),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O56))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E56),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O56))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F56),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O56))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G56),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O56))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H56),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J56" s="11" t="n"/>
@@ -5417,7 +5509,7 @@
       <c r="G57" s="5" t="n"/>
       <c r="H57" s="5" t="n"/>
       <c r="I57" s="19">
-        <f>IF($O57=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O57))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O57))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E57),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O57))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F57),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O57))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G57),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O57))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H57),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O57))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E57),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O57))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F57),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O57))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G57),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O57))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H57),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O57=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O57))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O57))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E57),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O57))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F57),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O57))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G57),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O57))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H57),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O57))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E57),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O57))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F57),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O57))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G57),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O57))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H57),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J57" s="11" t="n"/>
@@ -5450,7 +5542,7 @@
       <c r="G58" s="5" t="n"/>
       <c r="H58" s="5" t="n"/>
       <c r="I58" s="19">
-        <f>IF($O58=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O58))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O58))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E58),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O58))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F58),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O58))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G58),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O58))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H58),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O58))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E58),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O58))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F58),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O58))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G58),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O58))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H58),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O58=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O58))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O58))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E58),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O58))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F58),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O58))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G58),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O58))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H58),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O58))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E58),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O58))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F58),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O58))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G58),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O58))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H58),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J58" s="11" t="n"/>
@@ -5483,7 +5575,7 @@
       <c r="G59" s="5" t="n"/>
       <c r="H59" s="5" t="n"/>
       <c r="I59" s="19">
-        <f>IF($O59=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O59))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O59))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E59),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O59))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F59),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O59))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G59),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O59))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H59),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O59))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E59),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O59))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F59),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O59))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G59),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O59))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H59),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O59=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O59))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O59))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E59),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O59))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F59),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O59))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G59),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O59))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H59),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O59))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E59),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O59))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F59),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O59))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G59),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O59))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H59),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J59" s="11" t="n"/>
@@ -5516,7 +5608,7 @@
       <c r="G60" s="5" t="n"/>
       <c r="H60" s="5" t="n"/>
       <c r="I60" s="19">
-        <f>IF($O60=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O60))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O60))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E60),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O60))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F60),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O60))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G60),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O60))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H60),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O60))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E60),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O60))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F60),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O60))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G60),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O60))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H60),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O60=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O60))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O60))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E60),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O60))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F60),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O60))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G60),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O60))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H60),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O60))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E60),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O60))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F60),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O60))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G60),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O60))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H60),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J60" s="11" t="n"/>
@@ -5549,7 +5641,7 @@
       <c r="G61" s="5" t="n"/>
       <c r="H61" s="5" t="n"/>
       <c r="I61" s="19">
-        <f>IF($O61=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O61))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O61))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E61),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O61))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F61),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O61))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G61),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O61))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H61),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O61))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E61),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O61))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F61),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O61))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G61),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O61))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H61),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O61=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O61))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O61))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E61),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O61))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F61),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O61))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G61),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O61))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H61),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O61))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E61),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O61))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F61),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O61))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G61),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O61))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H61),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J61" s="11" t="n"/>
@@ -5582,7 +5674,7 @@
       <c r="G62" s="5" t="n"/>
       <c r="H62" s="5" t="n"/>
       <c r="I62" s="19">
-        <f>IF($O62=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O62))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O62))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E62),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O62))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F62),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O62))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G62),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O62))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H62),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O62))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E62),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O62))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F62),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O62))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G62),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O62))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H62),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O62=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O62))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O62))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E62),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O62))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F62),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O62))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G62),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O62))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H62),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O62))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E62),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O62))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F62),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O62))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G62),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O62))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H62),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J62" s="11" t="n"/>
@@ -5615,7 +5707,7 @@
       <c r="G63" s="5" t="n"/>
       <c r="H63" s="5" t="n"/>
       <c r="I63" s="19">
-        <f>IF($O63=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O63))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O63))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E63),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O63))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F63),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O63))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G63),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O63))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H63),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O63))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E63),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O63))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F63),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O63))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G63),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O63))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H63),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O63=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O63))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O63))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E63),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O63))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F63),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O63))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G63),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O63))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H63),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O63))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E63),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O63))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F63),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O63))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G63),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O63))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H63),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J63" s="11" t="n"/>
@@ -5648,7 +5740,7 @@
       <c r="G64" s="5" t="n"/>
       <c r="H64" s="5" t="n"/>
       <c r="I64" s="19">
-        <f>IF($O64=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O64))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O64))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E64),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O64))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F64),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O64))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G64),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O64))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H64),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O64))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E64),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O64))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F64),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O64))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G64),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O64))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H64),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O64=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O64))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O64))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E64),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O64))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F64),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O64))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G64),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O64))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H64),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O64))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E64),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O64))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F64),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O64))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G64),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O64))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H64),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J64" s="11" t="n"/>
@@ -5681,7 +5773,7 @@
       <c r="G65" s="5" t="n"/>
       <c r="H65" s="5" t="n"/>
       <c r="I65" s="19">
-        <f>IF($O65=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O65))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O65))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E65),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O65))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F65),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O65))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G65),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O65))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H65),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O65))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E65),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O65))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F65),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O65))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G65),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O65))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H65),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O65=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O65))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O65))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E65),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O65))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F65),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O65))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G65),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O65))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H65),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O65))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E65),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O65))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F65),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O65))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G65),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O65))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H65),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J65" s="11" t="n"/>
@@ -5714,7 +5806,7 @@
       <c r="G66" s="5" t="n"/>
       <c r="H66" s="5" t="n"/>
       <c r="I66" s="19">
-        <f>IF($O66=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O66))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O66))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E66),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O66))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F66),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O66))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G66),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O66))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H66),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O66))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E66),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O66))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F66),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O66))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G66),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O66))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H66),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O66=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O66))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O66))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E66),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O66))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F66),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O66))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G66),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O66))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H66),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O66))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E66),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O66))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F66),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O66))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G66),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O66))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H66),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J66" s="11" t="n"/>
@@ -5747,7 +5839,7 @@
       <c r="G67" s="5" t="n"/>
       <c r="H67" s="5" t="n"/>
       <c r="I67" s="19">
-        <f>IF($O67=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O67))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O67))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E67),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O67))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F67),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O67))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G67),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O67))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H67),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O67))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E67),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O67))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F67),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O67))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G67),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O67))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H67),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O67=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O67))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O67))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E67),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O67))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F67),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O67))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G67),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O67))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H67),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O67))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E67),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O67))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F67),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O67))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G67),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O67))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H67),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J67" s="11" t="n"/>
@@ -5780,7 +5872,7 @@
       <c r="G68" s="5" t="n"/>
       <c r="H68" s="5" t="n"/>
       <c r="I68" s="19">
-        <f>IF($O68=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O68))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O68))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E68),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O68))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F68),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O68))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G68),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O68))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H68),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O68))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E68),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O68))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F68),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O68))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G68),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O68))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H68),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O68=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O68))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O68))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E68),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O68))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F68),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O68))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G68),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O68))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H68),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O68))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E68),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O68))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F68),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O68))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G68),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O68))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H68),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J68" s="11" t="n"/>
@@ -5813,7 +5905,7 @@
       <c r="G69" s="5" t="n"/>
       <c r="H69" s="5" t="n"/>
       <c r="I69" s="19">
-        <f>IF($O69=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O69))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O69))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E69),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O69))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F69),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O69))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G69),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O69))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H69),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O69))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E69),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O69))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F69),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O69))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G69),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O69))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H69),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O69=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O69))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O69))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E69),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O69))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F69),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O69))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G69),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O69))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H69),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O69))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E69),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O69))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F69),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O69))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G69),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O69))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H69),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J69" s="11" t="n"/>
@@ -5846,7 +5938,7 @@
       <c r="G70" s="5" t="n"/>
       <c r="H70" s="5" t="n"/>
       <c r="I70" s="19">
-        <f>IF($O70=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O70))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O70))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E70),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O70))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F70),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O70))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G70),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O70))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H70),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O70))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E70),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O70))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F70),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O70))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G70),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O70))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H70),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O70=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O70))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O70))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E70),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O70))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F70),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O70))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G70),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O70))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H70),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O70))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E70),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O70))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F70),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O70))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G70),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O70))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H70),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J70" s="11" t="n"/>
@@ -5879,7 +5971,7 @@
       <c r="G71" s="5" t="n"/>
       <c r="H71" s="5" t="n"/>
       <c r="I71" s="19">
-        <f>IF($O71=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O71))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O71))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E71),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O71))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F71),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O71))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G71),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O71))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H71),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O71))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E71),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O71))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F71),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O71))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G71),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O71))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H71),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O71=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O71))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O71))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E71),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O71))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F71),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O71))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G71),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O71))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H71),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O71))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E71),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O71))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F71),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O71))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G71),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O71))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H71),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J71" s="11" t="n"/>
@@ -5912,7 +6004,7 @@
       <c r="G72" s="5" t="n"/>
       <c r="H72" s="5" t="n"/>
       <c r="I72" s="19">
-        <f>IF($O72=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O72))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O72))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E72),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O72))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F72),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O72))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G72),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O72))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H72),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O72))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E72),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O72))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F72),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O72))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G72),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O72))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H72),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O72=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O72))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O72))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E72),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O72))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F72),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O72))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G72),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O72))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H72),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O72))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E72),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O72))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F72),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O72))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G72),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O72))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H72),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J72" s="11" t="n"/>
@@ -5945,7 +6037,7 @@
       <c r="G73" s="5" t="n"/>
       <c r="H73" s="5" t="n"/>
       <c r="I73" s="19">
-        <f>IF($O73=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O73))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O73))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E73),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O73))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F73),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O73))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G73),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O73))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H73),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O73))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E73),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O73))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F73),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O73))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G73),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O73))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H73),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O73=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O73))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O73))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E73),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O73))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F73),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O73))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G73),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O73))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H73),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O73))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E73),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O73))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F73),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O73))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G73),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O73))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H73),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J73" s="11" t="n"/>
@@ -5978,7 +6070,7 @@
       <c r="G74" s="5" t="n"/>
       <c r="H74" s="5" t="n"/>
       <c r="I74" s="19">
-        <f>IF($O74=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O74))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O74))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E74),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O74))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F74),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O74))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G74),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O74))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H74),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O74))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E74),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O74))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F74),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O74))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G74),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O74))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H74),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O74=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O74))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O74))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E74),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O74))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F74),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O74))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G74),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O74))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H74),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O74))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E74),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O74))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F74),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O74))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G74),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O74))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H74),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J74" s="11" t="n"/>
@@ -6011,7 +6103,7 @@
       <c r="G75" s="5" t="n"/>
       <c r="H75" s="5" t="n"/>
       <c r="I75" s="19">
-        <f>IF($O75=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O75))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O75))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E75),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O75))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F75),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O75))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G75),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O75))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H75),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O75))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E75),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O75))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F75),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O75))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G75),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O75))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H75),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O75=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O75))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O75))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E75),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O75))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F75),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O75))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G75),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O75))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H75),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O75))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E75),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O75))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F75),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O75))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G75),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O75))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H75),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J75" s="11" t="n"/>
@@ -6044,7 +6136,7 @@
       <c r="G76" s="5" t="n"/>
       <c r="H76" s="5" t="n"/>
       <c r="I76" s="19">
-        <f>IF($O76=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O76))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O76))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E76),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O76))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F76),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O76))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G76),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O76))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H76),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O76))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E76),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O76))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F76),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O76))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G76),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O76))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H76),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O76=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O76))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O76))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E76),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O76))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F76),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O76))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G76),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O76))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H76),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O76))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E76),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O76))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F76),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O76))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G76),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O76))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H76),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J76" s="11" t="n"/>
@@ -6077,7 +6169,7 @@
       <c r="G77" s="5" t="n"/>
       <c r="H77" s="5" t="n"/>
       <c r="I77" s="19">
-        <f>IF($O77=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O77))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O77))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E77),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O77))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F77),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O77))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G77),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O77))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H77),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O77))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E77),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O77))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F77),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O77))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G77),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O77))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H77),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O77=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O77))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O77))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E77),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O77))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F77),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O77))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G77),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O77))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H77),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O77))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E77),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O77))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F77),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O77))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G77),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O77))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H77),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J77" s="11" t="n"/>
@@ -6110,7 +6202,7 @@
       <c r="G78" s="5" t="n"/>
       <c r="H78" s="5" t="n"/>
       <c r="I78" s="19">
-        <f>IF($O78=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O78))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O78))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E78),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O78))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F78),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O78))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G78),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O78))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H78),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O78))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E78),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O78))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F78),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O78))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G78),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O78))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H78),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O78=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O78))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O78))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E78),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O78))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F78),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O78))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G78),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O78))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H78),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O78))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E78),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O78))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F78),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O78))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G78),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O78))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H78),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J78" s="11" t="n"/>
@@ -6143,7 +6235,7 @@
       <c r="G79" s="5" t="n"/>
       <c r="H79" s="5" t="n"/>
       <c r="I79" s="19">
-        <f>IF($O79=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O79))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O79))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E79),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O79))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F79),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O79))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G79),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O79))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H79),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O79))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E79),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O79))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F79),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O79))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G79),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O79))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H79),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O79=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O79))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O79))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E79),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O79))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F79),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O79))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G79),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O79))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H79),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O79))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E79),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O79))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F79),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O79))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G79),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O79))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H79),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J79" s="11" t="n"/>
@@ -6176,7 +6268,7 @@
       <c r="G80" s="5" t="n"/>
       <c r="H80" s="5" t="n"/>
       <c r="I80" s="19">
-        <f>IF($O80=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O80))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O80))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E80),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O80))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F80),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O80))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G80),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O80))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H80),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O80))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E80),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O80))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F80),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O80))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G80),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O80))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H80),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O80=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O80))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O80))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E80),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O80))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F80),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O80))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G80),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O80))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H80),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O80))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E80),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O80))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F80),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O80))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G80),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O80))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H80),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J80" s="11" t="n"/>
@@ -6209,7 +6301,7 @@
       <c r="G81" s="5" t="n"/>
       <c r="H81" s="5" t="n"/>
       <c r="I81" s="19">
-        <f>IF($O81=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O81))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O81))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E81),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O81))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F81),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O81))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G81),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O81))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H81),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O81))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E81),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O81))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F81),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O81))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G81),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O81))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H81),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O81=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O81))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O81))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E81),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O81))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F81),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O81))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G81),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O81))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H81),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O81))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E81),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O81))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F81),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O81))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G81),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O81))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H81),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J81" s="11" t="n"/>
@@ -6242,7 +6334,7 @@
       <c r="G82" s="5" t="n"/>
       <c r="H82" s="5" t="n"/>
       <c r="I82" s="19">
-        <f>IF($O82=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O82))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O82))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E82),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O82))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F82),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O82))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G82),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O82))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H82),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O82))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E82),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O82))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F82),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O82))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G82),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O82))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H82),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O82=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O82))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O82))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E82),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O82))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F82),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O82))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G82),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O82))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H82),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O82))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E82),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O82))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F82),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O82))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G82),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O82))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H82),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J82" s="11" t="n"/>
@@ -6275,7 +6367,7 @@
       <c r="G83" s="5" t="n"/>
       <c r="H83" s="5" t="n"/>
       <c r="I83" s="19">
-        <f>IF($O83=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O83))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O83))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E83),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O83))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F83),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O83))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G83),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O83))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H83),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O83))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E83),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O83))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F83),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O83))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G83),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O83))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H83),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O83=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O83))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O83))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E83),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O83))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F83),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O83))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G83),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O83))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H83),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O83))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E83),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O83))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F83),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O83))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G83),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O83))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H83),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J83" s="11" t="n"/>
@@ -6308,7 +6400,7 @@
       <c r="G84" s="5" t="n"/>
       <c r="H84" s="5" t="n"/>
       <c r="I84" s="19">
-        <f>IF($O84=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O84))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O84))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E84),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O84))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F84),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O84))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G84),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O84))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H84),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O84))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E84),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O84))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F84),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O84))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G84),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O84))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H84),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O84=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O84))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O84))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E84),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O84))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F84),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O84))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G84),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O84))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H84),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O84))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E84),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O84))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F84),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O84))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G84),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O84))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H84),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J84" s="11" t="n"/>
@@ -6341,7 +6433,7 @@
       <c r="G85" s="5" t="n"/>
       <c r="H85" s="5" t="n"/>
       <c r="I85" s="19">
-        <f>IF($O85=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O85))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O85))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E85),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O85))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F85),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O85))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G85),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O85))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H85),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O85))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E85),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O85))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F85),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O85))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G85),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O85))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H85),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O85=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O85))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O85))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E85),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O85))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F85),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O85))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G85),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O85))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H85),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O85))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E85),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O85))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F85),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O85))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G85),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O85))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H85),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J85" s="11" t="n"/>
@@ -6374,7 +6466,7 @@
       <c r="G86" s="5" t="n"/>
       <c r="H86" s="5" t="n"/>
       <c r="I86" s="19">
-        <f>IF($O86=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O86))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O86))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E86),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O86))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F86),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O86))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G86),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O86))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H86),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O86))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E86),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O86))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F86),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O86))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G86),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O86))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H86),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O86=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O86))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O86))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E86),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O86))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F86),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O86))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G86),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O86))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H86),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O86))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E86),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O86))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F86),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O86))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G86),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O86))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H86),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J86" s="11" t="n"/>
@@ -6407,7 +6499,7 @@
       <c r="G87" s="5" t="n"/>
       <c r="H87" s="5" t="n"/>
       <c r="I87" s="19">
-        <f>IF($O87=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O87))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O87))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E87),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O87))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F87),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O87))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G87),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O87))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H87),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O87))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E87),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O87))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F87),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O87))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G87),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O87))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H87),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O87=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O87))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O87))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E87),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O87))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F87),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O87))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G87),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O87))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H87),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O87))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E87),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O87))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F87),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O87))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G87),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O87))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H87),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J87" s="11" t="n"/>
@@ -6440,7 +6532,7 @@
       <c r="G88" s="5" t="n"/>
       <c r="H88" s="5" t="n"/>
       <c r="I88" s="19">
-        <f>IF($O88=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O88))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O88))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E88),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O88))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F88),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O88))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G88),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O88))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H88),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O88))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E88),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O88))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F88),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O88))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G88),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O88))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H88),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O88=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O88))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O88))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E88),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O88))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F88),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O88))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G88),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O88))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H88),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O88))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E88),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O88))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F88),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O88))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G88),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O88))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H88),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J88" s="11" t="n"/>
@@ -6473,7 +6565,7 @@
       <c r="G89" s="5" t="n"/>
       <c r="H89" s="5" t="n"/>
       <c r="I89" s="19">
-        <f>IF($O89=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O89))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O89))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E89),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O89))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F89),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O89))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G89),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O89))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H89),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O89))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E89),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O89))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F89),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O89))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G89),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O89))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H89),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O89=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O89))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O89))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E89),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O89))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F89),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O89))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G89),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O89))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H89),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O89))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E89),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O89))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F89),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O89))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G89),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O89))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H89),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J89" s="11" t="n"/>
@@ -6506,7 +6598,7 @@
       <c r="G90" s="5" t="n"/>
       <c r="H90" s="5" t="n"/>
       <c r="I90" s="19">
-        <f>IF($O90=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O90))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O90))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E90),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O90))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F90),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O90))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G90),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O90))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H90),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O90))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E90),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O90))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F90),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O90))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G90),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O90))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H90),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O90=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O90))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O90))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E90),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O90))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F90),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O90))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G90),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O90))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H90),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O90))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E90),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O90))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F90),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O90))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G90),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O90))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H90),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J90" s="11" t="n"/>
@@ -6539,7 +6631,7 @@
       <c r="G91" s="5" t="n"/>
       <c r="H91" s="5" t="n"/>
       <c r="I91" s="19">
-        <f>IF($O91=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O91))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O91))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E91),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O91))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F91),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O91))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G91),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O91))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H91),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O91))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E91),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O91))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F91),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O91))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G91),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O91))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H91),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O91=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O91))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O91))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E91),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O91))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F91),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O91))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G91),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O91))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H91),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O91))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E91),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O91))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F91),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O91))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G91),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O91))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H91),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J91" s="11" t="n"/>
@@ -6572,7 +6664,7 @@
       <c r="G92" s="5" t="n"/>
       <c r="H92" s="5" t="n"/>
       <c r="I92" s="19">
-        <f>IF($O92=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O92))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O92))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E92),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O92))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F92),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O92))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G92),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O92))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H92),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O92))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E92),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O92))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F92),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O92))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G92),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O92))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H92),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O92=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O92))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O92))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E92),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O92))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F92),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O92))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G92),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O92))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H92),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O92))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E92),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O92))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F92),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O92))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G92),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O92))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H92),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J92" s="11" t="n"/>
@@ -6605,7 +6697,7 @@
       <c r="G93" s="5" t="n"/>
       <c r="H93" s="5" t="n"/>
       <c r="I93" s="19">
-        <f>IF($O93=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O93))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O93))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E93),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O93))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F93),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O93))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G93),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O93))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H93),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O93))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E93),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O93))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F93),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O93))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G93),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O93))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H93),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O93=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O93))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O93))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E93),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O93))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F93),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O93))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G93),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O93))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H93),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O93))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E93),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O93))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F93),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O93))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G93),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O93))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H93),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J93" s="11" t="n"/>
@@ -6638,7 +6730,7 @@
       <c r="G94" s="5" t="n"/>
       <c r="H94" s="5" t="n"/>
       <c r="I94" s="19">
-        <f>IF($O94=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O94))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O94))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E94),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O94))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F94),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O94))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G94),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O94))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H94),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O94))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E94),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O94))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F94),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O94))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G94),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O94))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H94),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O94=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O94))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O94))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E94),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O94))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F94),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O94))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G94),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O94))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H94),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O94))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E94),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O94))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F94),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O94))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G94),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O94))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H94),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J94" s="11" t="n"/>
@@ -6671,7 +6763,7 @@
       <c r="G95" s="5" t="n"/>
       <c r="H95" s="5" t="n"/>
       <c r="I95" s="19">
-        <f>IF($O95=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O95))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O95))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E95),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O95))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F95),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O95))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G95),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O95))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H95),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O95))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E95),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O95))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F95),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O95))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G95),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O95))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H95),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O95=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O95))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O95))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E95),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O95))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F95),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O95))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G95),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O95))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H95),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O95))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E95),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O95))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F95),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O95))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G95),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O95))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H95),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J95" s="11" t="n"/>
@@ -6704,7 +6796,7 @@
       <c r="G96" s="5" t="n"/>
       <c r="H96" s="5" t="n"/>
       <c r="I96" s="19">
-        <f>IF($O96=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O96))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O96))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E96),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O96))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F96),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O96))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G96),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O96))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H96),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O96))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E96),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O96))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F96),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O96))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G96),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O96))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H96),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O96=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O96))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O96))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E96),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O96))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F96),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O96))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G96),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O96))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H96),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O96))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E96),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O96))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F96),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O96))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G96),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O96))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H96),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J96" s="11" t="n"/>
@@ -6737,7 +6829,7 @@
       <c r="G97" s="5" t="n"/>
       <c r="H97" s="5" t="n"/>
       <c r="I97" s="19">
-        <f>IF($O97=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O97))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O97))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E97),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O97))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F97),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O97))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G97),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O97))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H97),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O97))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E97),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O97))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F97),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O97))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G97),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O97))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H97),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O97=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O97))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O97))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E97),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O97))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F97),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O97))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G97),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O97))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H97),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O97))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E97),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O97))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F97),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O97))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G97),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O97))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H97),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J97" s="11" t="n"/>
@@ -6770,7 +6862,7 @@
       <c r="G98" s="5" t="n"/>
       <c r="H98" s="5" t="n"/>
       <c r="I98" s="19">
-        <f>IF($O98=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O98))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O98))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E98),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O98))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F98),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O98))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G98),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O98))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H98),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O98))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E98),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O98))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F98),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O98))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G98),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O98))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H98),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O98=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O98))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O98))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E98),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O98))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F98),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O98))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G98),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O98))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H98),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O98))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E98),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O98))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F98),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O98))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G98),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O98))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H98),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J98" s="11" t="n"/>
@@ -6803,7 +6895,7 @@
       <c r="G99" s="5" t="n"/>
       <c r="H99" s="5" t="n"/>
       <c r="I99" s="19">
-        <f>IF($O99=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O99))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O99))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E99),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O99))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F99),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O99))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G99),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O99))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H99),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O99))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E99),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O99))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F99),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O99))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G99),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O99))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H99),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O99=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O99))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O99))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E99),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O99))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F99),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O99))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G99),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O99))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H99),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O99))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E99),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O99))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F99),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O99))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G99),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O99))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H99),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J99" s="11" t="n"/>
@@ -6836,7 +6928,7 @@
       <c r="G100" s="5" t="n"/>
       <c r="H100" s="5" t="n"/>
       <c r="I100" s="19">
-        <f>IF($O100=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O100))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O100))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E100),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O100))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F100),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O100))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G100),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O100))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H100),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O100))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E100),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O100))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F100),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O100))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G100),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O100))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H100),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O100=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O100))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O100))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E100),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O100))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F100),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O100))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G100),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O100))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H100),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O100))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E100),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O100))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F100),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O100))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G100),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O100))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H100),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J100" s="11" t="n"/>
@@ -6869,7 +6961,7 @@
       <c r="G101" s="5" t="n"/>
       <c r="H101" s="5" t="n"/>
       <c r="I101" s="19">
-        <f>IF($O101=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O101))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O101))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E101),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O101))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F101),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O101))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G101),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O101))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H101),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O101))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E101),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O101))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F101),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O101))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G101),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O101))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H101),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O101=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O101))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O101))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E101),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O101))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F101),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O101))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G101),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O101))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H101),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O101))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E101),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O101))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F101),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O101))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G101),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O101))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H101),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J101" s="11" t="n"/>
@@ -6902,7 +6994,7 @@
       <c r="G102" s="5" t="n"/>
       <c r="H102" s="5" t="n"/>
       <c r="I102" s="19">
-        <f>IF($O102=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O102))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O102))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E102),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O102))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F102),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O102))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G102),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O102))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H102),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O102))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E102),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O102))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F102),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O102))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G102),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O102))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H102),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O102=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O102))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O102))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E102),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O102))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F102),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O102))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G102),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O102))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H102),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O102))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E102),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O102))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F102),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O102))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G102),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O102))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H102),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J102" s="11" t="n"/>
@@ -6935,7 +7027,7 @@
       <c r="G103" s="5" t="n"/>
       <c r="H103" s="5" t="n"/>
       <c r="I103" s="19">
-        <f>IF($O103=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O103))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O103))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E103),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O103))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F103),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O103))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G103),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O103))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H103),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O103))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E103),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O103))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F103),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O103))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G103),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O103))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H103),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O103=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O103))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O103))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E103),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O103))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F103),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O103))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G103),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O103))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H103),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O103))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E103),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O103))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F103),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O103))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G103),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O103))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H103),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J103" s="11" t="n"/>
@@ -6968,7 +7060,7 @@
       <c r="G104" s="5" t="n"/>
       <c r="H104" s="5" t="n"/>
       <c r="I104" s="19">
-        <f>IF($O104=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O104))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O104))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E104),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O104))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F104),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O104))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G104),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O104))="Sí",SUMIFS(Ajustes!$D$5:$D$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H104),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O104))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Largo",Ajustes!$B$5:$B$19,""&amp;$E104),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O104))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Densidad",Ajustes!$B$5:$B$19,""&amp;$F104),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O104))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Estado de la fibra",Ajustes!$B$5:$B$19,""&amp;$G104),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O104))="Sí",SUMIFS(Ajustes!$E$5:$E$19,Ajustes!$A$5:$A$19,"Canas",Ajustes!$B$5:$B$19,""&amp;$H104),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
+        <f>IF($O104=0,"",ROUND((INDEX(Servicios!$C$9:$C$38,MAX(1,$O104))+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O104))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E104),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O104))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F104),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O104))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G104),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O104))="Sí",SUMIFS(Ajustes!$D$5:$D$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H104),0))*(1+IF(INDEX(Servicios!$D$9:$D$38,MAX(1,$O104))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Largo",Ajustes!$B$5:$B$18,""&amp;$E104),0)+IF(INDEX(Servicios!$E$9:$E$38,MAX(1,$O104))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Densidad",Ajustes!$B$5:$B$18,""&amp;$F104),0)+IF(INDEX(Servicios!$F$9:$F$38,MAX(1,$O104))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Estado de la fibra",Ajustes!$B$5:$B$18,""&amp;$G104),0)+IF(INDEX(Servicios!$G$9:$G$38,MAX(1,$O104))="Sí",SUMIFS(Ajustes!$E$5:$E$18,Ajustes!$A$5:$A$18,"Canas",Ajustes!$B$5:$B$18,""&amp;$H104),0))/MAX(1,Servicios!$E$5),0)*MAX(1,Servicios!$E$5))</f>
         <v/>
       </c>
       <c r="J104" s="11" t="n"/>
@@ -7012,7 +7104,7 @@
       <formula1>Ajustes!$B$12:$B$14</formula1>
     </dataValidation>
     <dataValidation sqref="H5:H104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista." type="list">
-      <formula1>Ajustes!$B$15:$B$19</formula1>
+      <formula1>Ajustes!$B$15:$B$18</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
